--- a/docs/ThermoGuard_UI_명세서_테이블_최신본.xlsx
+++ b/docs/ThermoGuard_UI_명세서_테이블_최신본.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="650">
   <si>
     <t xml:space="preserve">항목</t>
   </si>
@@ -1222,26 +1222,66 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 알림 팝업을 열고 </t>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 선택 가능한 알림 팝업을 열고 </t>
     </r>
     <r>
       <rPr>
@@ -1270,7 +1310,7 @@
     <t xml:space="preserve">list[dict[str, Any]]</t>
   </si>
   <si>
-    <t xml:space="preserve">Tkinter command → GET /api/alerts?days=7</t>
+    <t xml:space="preserve">Tkinter command → GET /api/alerts?hours={1|24|72|168}</t>
   </si>
   <si>
     <r>
@@ -1360,7 +1400,7 @@
     <t xml:space="preserve">list[tuple[datetime, float]]</t>
   </si>
   <si>
-    <t xml:space="preserve">Tkinter command → GET /api/temperature-trend?days=7</t>
+    <t xml:space="preserve">Tkinter command → GET /api/temperature-trend?hours={1|24|72|168}</t>
   </si>
   <si>
     <r>
@@ -6476,24 +6516,61 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">고정 안내</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 시각 기준 최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ 7</t>
     </r>
     <r>
       <rPr>
@@ -6505,9 +6582,36 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">알림 이력 범위 확인</t>
-  </si>
-  <si>
+    <t xml:space="preserve">기간 선택</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알림 이력 범위 선택</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택값을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">hours=1·24·72·168</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 변환해 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6522,33 +6626,133 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">요청에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">days=7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 고정 적용</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
+      <t xml:space="preserve">요청</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">alert_history_hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._on_alert_period_changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tkinter Combobox → hours=1|24|72|168</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필터</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미확인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 완료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">필터 선택</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알림 처리 상태별 조회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선택한 기간 범위 안에서 상태별로 즉시 필터링</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alert_filter_var</t>
   </si>
   <si>
     <t xml:space="preserve">ProductDashboard._render_alert_cards</t>
   </si>
   <si>
-    <t xml:space="preserve">GET /api/alerts?days=7&amp;limit=5000</t>
+    <t xml:space="preserve">tk.StringVar</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 메모리 필터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통신 없음</t>
+    </r>
   </si>
   <si>
     <r>
@@ -6577,42 +6781,884 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">필터</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미확인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 완료 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
+      <t xml:space="preserve">새로고침</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">새로고침</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Backend </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 기간 알림 재조회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">GET /api/alerts?hours={1|24|72|168}&amp;limit=5000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후 목록 갱신</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">alerts_response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._refresh_alert_history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP GET /api/alerts?hours={1|24|72|168}&amp;limit=5000 → alert_events</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림 목록</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발생 시각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·ROI·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대 온도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 상태</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Backend </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">및 로컬 선택 기간 이벤트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">알림 현황 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시간 역순 정렬하고 선택 기간 이전 항목 제외</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._merge_backend_alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REST JSON → Tkinter Treeview</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 알림 확인 처리</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 알림 확인 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">테이블 행 선택 후 클릭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">운영자가 알림을 확인했음을 기록</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">PATCH /api/alerts/{alert_id} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성공 후 확인 완료로 갱신</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">alert_events.event_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._acknowledge_selected_alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP PATCH /api/alerts/{alert_id} → alert_events</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그래프팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회 범위</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">과거 온도 변화 범위 선택</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">GET /api/temperature-trend?hours={1|24|72|168}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기록 조회</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_history_hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._on_trend_period_changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tkinter Combobox → GET /api/temperature-trend?hours={1|24|72|168}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그래프팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 상태 게이지</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Canvas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주황</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빨강</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 최대온도</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">최신 분석 상태와 온도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현재 위험 수준을 직관적으로 확인</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">새 분석 결과와 설정 임계값에 따라 바늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">색상 갱신</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">latest_status + temperature_history[-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._draw_status_gauge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status + tuple[datetime, float]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 분석 상태 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tkinter Canvas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그래프팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">온도 그래프</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Canvas</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 기간 전체 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대온도 선 그래프</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과거 기록 및 실시간 측정값</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 기간 온도 변화와 급상승 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 기간으로 필터링하고 촬영시각 중복 제거 후 실시간 값을 이어 붙임</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._draw_temperature_trend</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">REST JSON + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실시간 메모리 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tkinter Canvas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그래프팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터 축약</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">표시 처리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 표시점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 기간 원본 측정값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대용량 그래프 성능 유지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시간 구간별 최고온도를 보존해 표시점 축약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">display_history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._downsample_temperature_history</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 메모리 연산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통신 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그래프팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준선</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">그래프 보조선</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험 기준선</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Threshold</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">판정 기준과 측정값 비교</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설정 변경 또는 그래프 갱신 시 위치와 라벨 다시 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">threshold_lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tuple[float, float]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAML Threshold → Tkinter Canvas</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운영로그</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그 필터</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">콤보박스 또는 탭</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6621,53 +7667,72 @@
       </rPr>
       <t xml:space="preserve">전체</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">필터 선택</t>
-  </si>
-  <si>
-    <t xml:space="preserve">알림 처리 상태별 조회</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선택 상태에 맞춰 최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 목록을 즉시 필터링</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">alert_filter_var</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tk.StringVar</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 메모리 필터 </t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·Backend·Telegram·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">환경설정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">원하는 로그 유형 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 범주로 운영 로그 필터링</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_category</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미구현 </t>
     </r>
     <r>
       <rPr>
@@ -6683,18 +7748,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">통신 없음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림팝업</t>
+      <t xml:space="preserve">현재 전체 로컬 메모리 목록 표시</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운영로그</t>
     </r>
     <r>
       <rPr>
@@ -6713,13 +7778,1193 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">새로고침</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">새로고침</t>
-  </si>
-  <si>
+      <t xml:space="preserve">로그 목록</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">런타임 로그</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시스템 동작 추적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최신 로그 추가 및 시간 역순 표시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._add_operating_log</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 메모리 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">+ Python logging</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 설정 저장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">파일 저장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config.yaml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">환경설정 입력값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">앱 재시작 후에도 설정 유지</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">환경설정 저장 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">AppConfig </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체를 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">YAML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 직렬화</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">cfg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">save_config</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">YAML </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 쓰기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설비 계층 조회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">REST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 카메라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상위 설비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라 코드 또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">IP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중복 등록 방지 및 내부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">FK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확보</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라 목록에서 일치 항목을 찾아 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">factory·line·robot·camera ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">asset_registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asset_api_client._find_asset_hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetRegistration | None</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HTTP GET /api/cameras → cameras + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">JOIN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설비 계층 등록</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">REST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식별자</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기존 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 내부 기본 식별값</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">측정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림 저장에 필요한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">FK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구성</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">누락된 계층만 공장→라인→로봇→카메라 순서로 생성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">factory_id + line_id + robot_id + camera_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asset_api_client.register_asset_hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetRegistration</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HTTP POST /api/factories·production-lines·robots·cameras → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테이블</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ROI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">REST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">좌표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·DB ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">편집 결과</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감시영역을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 일치시킴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">기존 좌표는 재사용하고 변경 좌표는 새 버전으로 생성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roi_definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roi_api_client.sync_rois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP GET/POST /api/rois → roi_definitions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/Threshold </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정상 온도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고폭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험폭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핫스팟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재전송 제한</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">환경설정 온도 기준</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">별 판정 기준을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Backend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 즉시 적용</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">활성 프로필이 있으면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">PATCH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하고 없으면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">POST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 생성</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">threshold_profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">threshold_api_client.sync_threshold_profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP GET/POST/PATCH /api/thresholds → threshold_profiles</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">측정 결과 저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">온도 통계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분석 버전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알람 여부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분석 결과</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">촬영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">측정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림 이력 영구 저장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마다 측정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">POST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6734,61 +8979,27 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 알림 재조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">GET /api/alerts?days=7&amp;limit=5000 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">후 목록 갱신</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">alerts_response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._refresh_alert_history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP GET /api/alerts?days=7&amp;limit=5000 → alert_events</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림팝업</t>
+      <t xml:space="preserve">트랜잭션에서 관련 테이블 생성</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">measurement_payload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TelegramDispatcher.post_measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP POST /api/measurements → captures·analysis_runs·roi_measurements·alert_events</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
     </r>
     <r>
       <rPr>
@@ -6807,33 +9018,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">알림 목록</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">발생 시각</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·ROI·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최대 온도</t>
+      <t xml:space="preserve">알림 이력 조회</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선택 기간 알림 목록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hours=1|24|72|168, limit=5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">알림 팝업 데이터 복원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Backend alert_events</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 선택 기간</t>
     </r>
     <r>
       <rPr>
@@ -6849,103 +9061,27 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 상태</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Backend </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">및 로컬 최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 이벤트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">알림 현황 확인</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시간 역순 정렬하고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 이전 항목 제외</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._merge_backend_alerts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REST JSON → Tkinter Treeview</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림팝업</t>
+      <t xml:space="preserve">시간 역순으로 조회해 로컬 이벤트와 병합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">alert_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._sync_events_from_backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP GET /api/alerts?hours={1|24|72|168} → alert_events</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
     </r>
     <r>
       <rPr>
@@ -6964,54 +9100,129 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선택 알림 확인 처리</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">선택 알림 확인 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">테이블 행 선택 후 클릭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">운영자가 알림을 확인했음을 기록</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PATCH /api/alerts/{alert_id} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">성공 후 확인 완료로 갱신</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">alert_events.event_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._acknowledge_selected_alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP PATCH /api/alerts/{alert_id} → alert_events</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그래프팝업</t>
+      <t xml:space="preserve">알림 확인 처리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">REST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">open / acknowledged / resolved</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">alert_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 상태</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">운영자의 알림 처리 기록 저장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 알림을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">PATCH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">acknowledged_at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">resolved_at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기록</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDashboard._acknowledge_event_backend</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF17365D"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터연동</t>
     </r>
     <r>
       <rPr>
@@ -7030,2358 +9241,75 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">조회 범위</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">고정 정책</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최근 최대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">과거 온도 변화 확인</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">GET /api/temperature-trend?days=7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기록 조회</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TREND_HISTORY_DAYS</t>
+      <t xml:space="preserve">온도 이력 조회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">촬영별 전체 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ROI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대온도</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">hours=1|24|72|168, limit=150000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">앱 재실행 후 선택 기간 그래프 복원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 기간 측정값을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">capture_id·measured_at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위로 집계해 반환</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">roi_measurements.max_temp</t>
   </si>
   <si>
     <t xml:space="preserve">ProductDashboard._sync_temperature_history</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP GET /api/temperature-trend?days=7 → roi_measurements</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그래프팝업</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 상태 게이지</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Canvas</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">초록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주황</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빨강</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 최대온도</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">최신 분석 상태와 온도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현재 위험 수준을 직관적으로 확인</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">새 분석 결과와 설정 임계값에 따라 바늘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">색상 갱신</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">latest_status + temperature_history[-1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._draw_status_gauge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status + tuple[datetime, float]</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 분석 상태 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Tkinter Canvas</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그래프팝업</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">온도 그래프</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Canvas</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 전체 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최대온도 선 그래프</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과거 기록 및 실시간 측정값</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">장기간 온도 변화와 급상승 확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">촬영시각 기준 중복 제거 후 과거 기록 뒤에 실시간 값을 이어 붙임</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._draw_temperature_trend</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">REST JSON + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실시간 메모리 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Tkinter Canvas</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그래프팝업</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터 축약</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">표시 처리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 표시점</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 원본 측정값</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">대용량 그래프 성능 유지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시간 구간별 최고온도를 보존해 표시점 축약</t>
-  </si>
-  <si>
-    <t xml:space="preserve">display_history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._downsample_temperature_history</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 메모리 연산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통신 없음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그래프팝업</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준선</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">그래프 보조선</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험 기준선</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Threshold</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">판정 기준과 측정값 비교</t>
-  </si>
-  <si>
-    <t xml:space="preserve">설정 변경 또는 그래프 갱신 시 위치와 라벨 다시 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">threshold_lines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tuple[float, float]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAML Threshold → Tkinter Canvas</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">운영로그</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로그 필터</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">콤보박스 또는 탭</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카메라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·Backend·Telegram·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">환경설정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">원하는 로그 유형 확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">선택 범주로 운영 로그 필터링</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_category</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미구현 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 전체 로컬 메모리 목록 표시</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">운영로그</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로그 목록</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시각</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상세</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">런타임 로그</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시스템 동작 추적</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최신 로그 추가 및 시간 역순 표시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._add_operating_log</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 메모리 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">+ Python logging</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 설정 저장</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">파일 저장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">config.yaml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">환경설정 입력값</t>
-  </si>
-  <si>
-    <t xml:space="preserve">앱 재시작 후에도 설정 유지</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">환경설정 저장 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">AppConfig </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체를 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">YAML</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 직렬화</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">cfg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">save_config</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">YAML </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파일 쓰기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">설비 계층 조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">REST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기존 카메라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상위 설비 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카메라 코드 또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">IP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중복 등록 방지 및 내부 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">FK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확보</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카메라 목록에서 일치 항목을 찾아 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">factory·line·robot·camera ID </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">복원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">asset_registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asset_api_client._find_asset_hierarchy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AssetRegistration | None</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">HTTP GET /api/cameras → cameras + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">JOIN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">설비 계층 등록</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">REST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내부 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">식별자</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기존 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ID </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 내부 기본 식별값</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">측정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림 저장에 필요한 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">FK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구성</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">누락된 계층만 공장→라인→로봇→카메라 순서로 생성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">factory_id + line_id + robot_id + camera_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asset_api_client.register_asset_hierarchy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AssetRegistration</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">HTTP POST /api/factories·production-lines·robots·cameras → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">각 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">테이블</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ROI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">REST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이름</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">좌표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">버전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·DB ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">편집 결과</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">감시영역을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">와 일치시킴</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">기존 좌표는 재사용하고 변경 좌표는 새 버전으로 생성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roi_definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roi_api_client.sync_rois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP GET/POST /api/rois → roi_definitions</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/Threshold </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정상 온도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고폭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험폭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">핫스팟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">재전송 제한</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">환경설정 온도 기준</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">별 판정 기준을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Backend</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 즉시 적용</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">활성 프로필이 있으면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PATCH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하고 없으면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">POST</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 생성</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">threshold_profiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">threshold_api_client.sync_threshold_profiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP GET/POST/PATCH /api/thresholds → threshold_profiles</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">측정 결과 저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">온도 통계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분석 버전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알람 여부</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분석 결과</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">촬영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">측정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림 이력 영구 저장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마다 측정 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">POST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">후 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Backend </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트랜잭션에서 관련 테이블 생성</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">measurement_payload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TelegramDispatcher.post_measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP POST /api/measurements → captures·analysis_runs·roi_measurements·alert_events</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림 이력 조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 알림 목록</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">days=7, limit=5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">알림 팝업 데이터 복원</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Backend alert_events</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">를 시간 역순으로 조회해 로컬 이벤트와 병합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">alert_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._sync_events_from_backend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP GET /api/alerts?days=7 → alert_events</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림 확인 처리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">REST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">open / acknowledged / resolved</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선택 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">alert_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">와 상태</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">운영자의 알림 처리 기록 저장</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선택 알림을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PATCH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">acknowledged_at </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">resolved_at </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기록</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ProductDashboard._acknowledge_event_backend</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">데이터연동</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF17365D"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">온도 이력 조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">촬영별 전체 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ROI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최대온도</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">days=7, limit=150000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">앱 재실행 후 과거 그래프 복원</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최근 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 측정값을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">capture_id·measured_at </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단위로 집계해 반환</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">roi_measurements.max_temp</t>
+    <t xml:space="preserve">HTTP GET /api/temperature-trend?hours={1|24|72|168} → roi_measurements</t>
   </si>
   <si>
     <r>
@@ -9912,9 +9840,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -10037,7 +9964,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10067,10 +9994,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10842,7 +10765,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>113</v>
       </c>
@@ -10858,7 +10781,7 @@
       <c r="E15" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>116</v>
       </c>
       <c r="G15" s="7" t="s">
@@ -11070,25 +10993,25 @@
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>529</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>455</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>532</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>74</v>
@@ -11097,39 +11020,39 @@
         <v>18</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>256</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>537</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>538</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>75</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -11200,418 +11123,418 @@
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>548</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>223</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>558</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>576</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>577</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>119</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>585</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>119</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>592</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>593</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>156</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>601</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>119</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>608</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>609</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>119</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>490</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>156</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>156</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>274</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>276</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -13388,26 +13311,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>445</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>450</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -13443,109 +13366,109 @@
         <v>458</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>119</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>256</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>117</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>119</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -13614,164 +13537,164 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C2" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>317</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>499</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>127</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>515</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>516</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>127</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>526</v>
       </c>
     </row>
   </sheetData>
